--- a/public/planilhas/07_bi_executivo_negocio.xlsx
+++ b/public/planilhas/07_bi_executivo_negocio.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DADOS_MENSAIS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,12 +19,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0x"/>
+    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;—&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +122,42 @@
       <color rgb="00C99C66"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00F3ECDD"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00C99C66"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -170,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -217,10 +255,25 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="15" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -228,6 +281,24 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="0043D07F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="00D9534F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -496,6 +567,219 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cascata · MRR bridge</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$30:$B$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$30:$C$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!D29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E9E5B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$30:$B$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$D$30:$D$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!E29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D9534F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$30:$B$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$E$30:$E$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!O29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15000">
+              <a:solidFill>
+                <a:srgbClr val="C99C66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$N$30:$N$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$O$30:$O$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -537,6 +821,50 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3600000" cy="1440000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -834,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:Z60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -956,27 +1284,27 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="7">
-        <f>B40</f>
+        <f>Z40</f>
         <v/>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="8">
-        <f>B41</f>
+        <f>Z41</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="9">
-        <f>B42</f>
+        <f>Z42</f>
         <v/>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="10">
-        <f>B43</f>
+        <f>Z43</f>
         <v/>
       </c>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="11">
-        <f>B45</f>
+        <f>Z45</f>
         <v/>
       </c>
       <c r="K6" s="6" t="n"/>
@@ -1047,17 +1375,17 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="13">
-        <f>B46</f>
+        <f>Z46</f>
         <v/>
       </c>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="14">
-        <f>B44</f>
+        <f>Z44</f>
         <v/>
       </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="14">
-        <f>B47</f>
+        <f>Z47</f>
         <v/>
       </c>
       <c r="G10" s="6" t="n"/>
@@ -1098,7 +1426,7 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="15">
-        <f>CONCATENATE("Leitura executiva: MRR de ",TEXT(B40,"R$ #,##0")," (",TEXT(B41,"+0.0%;-0.0%")," no mês). LTV/CAC de ",TEXT(B45,"0.0"),"x e churn de ",TEXT(B42,"0.0%"),". ",IF(B45&gt;=3,"Motor de aquisição saudável — pise no acelerador.",IF(B45&gt;=1,"Aquisição no limite — otimize CAC ou retenção.","Aquisição no vermelho — reduza CAC antes de escalar.")))</f>
+        <f>CONCATENATE("Leitura executiva: MRR de ",TEXT(Z40,"R$ #,##0")," (",TEXT(Z41,"+0.0%;-0.0%")," no mês). LTV/CAC de ",TEXT(Z45,"0.0"),"x e churn de ",TEXT(Z42,"0.0%"),". ",IF(Z45&gt;=3,"Motor de aquisição saudável — pise no acelerador.",IF(Z45&gt;=1,"Aquisição no limite — otimize CAC ou retenção.","Aquisição no vermelho — reduza CAC antes de escalar.")))</f>
         <v/>
       </c>
       <c r="C13" s="16" t="n"/>
@@ -1318,7 +1646,11 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Cascata do MRR (mês)</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
@@ -1329,76 +1661,246 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-    </row>
-    <row r="29">
+      <c r="N28" s="18" t="inlineStr">
+        <is>
+          <t>Spark · MRR 7 meses</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Ponto</t>
+        </is>
+      </c>
+      <c r="O29" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="P29" s="20" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>MRR anterior</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="22">
+        <f>IF(G30&gt;=0,G30,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="22">
+        <f>IF(G30&lt;0,-G30,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="22">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="G30" s="23">
+        <f>INDEX(DADOS_MENSAIS!E:E,11)</f>
+        <v/>
+      </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
+      <c r="N30" s="24" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="O30" s="25">
+        <f>DADOS_MENSAIS!E6</f>
+        <v/>
+      </c>
+      <c r="P30" s="26">
+        <f>IF(OR(O30="",NOT(ISNUMBER(O30))),"",REPT("▬",MAX(1,ROUND((O30-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>+ Expansão/novos</t>
+        </is>
+      </c>
+      <c r="C31" s="22">
+        <f>IF(G31&gt;=0,F30,F30+G31)</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f>IF(G31&gt;=0,G31,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="22">
+        <f>IF(G31&lt;0,-G31,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="22">
+        <f>F30+G31</f>
+        <v/>
+      </c>
+      <c r="G31" s="23">
+        <f>MAX(0,INDEX(DADOS_MENSAIS!E:E,12)-INDEX(DADOS_MENSAIS!E:E,11))</f>
+        <v/>
+      </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
+      <c r="N31" s="24" t="inlineStr">
+        <is>
+          <t>Fev</t>
+        </is>
+      </c>
+      <c r="O31" s="25">
+        <f>DADOS_MENSAIS!E7</f>
+        <v/>
+      </c>
+      <c r="P31" s="26">
+        <f>IF(OR(O31="",NOT(ISNUMBER(O31))),"",REPT("▬",MAX(1,ROUND((O31-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>− Contração</t>
+        </is>
+      </c>
+      <c r="C32" s="22">
+        <f>IF(G32&gt;=0,F31,F31+G32)</f>
+        <v/>
+      </c>
+      <c r="D32" s="22">
+        <f>IF(G32&gt;=0,G32,0)</f>
+        <v/>
+      </c>
+      <c r="E32" s="22">
+        <f>IF(G32&lt;0,-G32,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="22">
+        <f>F31+G32</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>MIN(0,INDEX(DADOS_MENSAIS!E:E,12)-INDEX(DADOS_MENSAIS!E:E,11))</f>
+        <v/>
+      </c>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
+      <c r="N32" s="24" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="O32" s="25">
+        <f>DADOS_MENSAIS!E8</f>
+        <v/>
+      </c>
+      <c r="P32" s="26">
+        <f>IF(OR(O32="",NOT(ISNUMBER(O32))),"",REPT("▬",MAX(1,ROUND((O32-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>MRR atual</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="22">
+        <f>IF(G33&gt;=0,G33,0)</f>
+        <v/>
+      </c>
+      <c r="E33" s="22">
+        <f>IF(G33&lt;0,-G33,0)</f>
+        <v/>
+      </c>
+      <c r="F33" s="22">
+        <f>G33</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>INDEX(DADOS_MENSAIS!E:E,12)</f>
+        <v/>
+      </c>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
+      <c r="N33" s="24" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="O33" s="25">
+        <f>DADOS_MENSAIS!E9</f>
+        <v/>
+      </c>
+      <c r="P33" s="26">
+        <f>IF(OR(O33="",NOT(ISNUMBER(O33))),"",REPT("▬",MAX(1,ROUND((O33-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1413,6 +1915,19 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
+      <c r="N34" s="24" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="O34" s="25">
+        <f>DADOS_MENSAIS!E10</f>
+        <v/>
+      </c>
+      <c r="P34" s="26">
+        <f>IF(OR(O34="",NOT(ISNUMBER(O34))),"",REPT("▬",MAX(1,ROUND((O34-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1427,6 +1942,19 @@
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
+      <c r="N35" s="24" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="O35" s="25">
+        <f>DADOS_MENSAIS!E11</f>
+        <v/>
+      </c>
+      <c r="P35" s="26">
+        <f>IF(OR(O35="",NOT(ISNUMBER(O35))),"",REPT("▬",MAX(1,ROUND((O35-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1441,6 +1969,19 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
+      <c r="N36" s="24" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="O36" s="25">
+        <f>DADOS_MENSAIS!E12</f>
+        <v/>
+      </c>
+      <c r="P36" s="26">
+        <f>IF(OR(O36="",NOT(ISNUMBER(O36))),"",REPT("▬",MAX(1,ROUND((O36-(MIN(O30:O36)))/MAX(1E-9,(MAX(O30:O36))-(MIN(O30:O36)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1458,7 +1999,11 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>MINI-SPARKLINES</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
@@ -1470,94 +2015,223 @@
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Atual</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="18">
-        <f>INDEX(DADOS_MENSAIS!E:E,12)</f>
-        <v/>
-      </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="C40" s="27">
+        <f>$Z$40</f>
+        <v/>
+      </c>
+      <c r="D40" s="28" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>22400</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>27200</v>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>30100</v>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>35600</v>
+      </c>
+      <c r="I40" s="28">
+        <f>$Z$40</f>
+        <v/>
+      </c>
+      <c r="J40" s="29">
+        <f>IF(D40=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D40-(MIN(D40:I40)))/MAX(1E-9,(MAX(D40:I40))-(MIN(D40:I40)))*7+1,0))),1))&amp;IF(E40=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E40-(MIN(D40:I40)))/MAX(1E-9,(MAX(D40:I40))-(MIN(D40:I40)))*7+1,0))),1))&amp;IF(F40=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F40-(MIN(D40:I40)))/MAX(1E-9,(MAX(D40:I40))-(MIN(D40:I40)))*7+1,0))),1))&amp;IF(G40=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G40-(MIN(D40:I40)))/MAX(1E-9,(MAX(D40:I40))-(MIN(D40:I40)))*7+1,0))),1))&amp;IF(H40=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H40-(MIN(D40:I40)))/MAX(1E-9,(MAX(D40:I40))-(MIN(D40:I40)))*7+1,0))),1))&amp;IF(I40=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I40-(MIN(D40:I40)))/MAX(1E-9,(MAX(D40:I40))-(MIN(D40:I40)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
+      <c r="Z40" s="30">
+        <f>INDEX(DADOS_MENSAIS!E:E,12)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="18">
-        <f>IFERROR(INDEX(DADOS_MENSAIS!E:E,12)/INDEX(DADOS_MENSAIS!E:E,11)-1,0)</f>
-        <v/>
-      </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Churn %</t>
+        </is>
+      </c>
+      <c r="C41" s="27">
+        <f>$Z$42*100</f>
+        <v/>
+      </c>
+      <c r="D41" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F41" s="28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G41" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I41" s="28">
+        <f>$Z$42*100</f>
+        <v/>
+      </c>
+      <c r="J41" s="29">
+        <f>IF(D41=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D41-(MIN(D41:I41)))/MAX(1E-9,(MAX(D41:I41))-(MIN(D41:I41)))*7+1,0))),1))&amp;IF(E41=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E41-(MIN(D41:I41)))/MAX(1E-9,(MAX(D41:I41))-(MIN(D41:I41)))*7+1,0))),1))&amp;IF(F41=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F41-(MIN(D41:I41)))/MAX(1E-9,(MAX(D41:I41))-(MIN(D41:I41)))*7+1,0))),1))&amp;IF(G41=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G41-(MIN(D41:I41)))/MAX(1E-9,(MAX(D41:I41))-(MIN(D41:I41)))*7+1,0))),1))&amp;IF(H41=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H41-(MIN(D41:I41)))/MAX(1E-9,(MAX(D41:I41))-(MIN(D41:I41)))*7+1,0))),1))&amp;IF(I41=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I41-(MIN(D41:I41)))/MAX(1E-9,(MAX(D41:I41))-(MIN(D41:I41)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
+      <c r="Z41" s="30">
+        <f>IFERROR(INDEX(DADOS_MENSAIS!E:E,12)/INDEX(DADOS_MENSAIS!E:E,11)-1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="18">
-        <f>IFERROR(INDEX(DADOS_MENSAIS!C:C,12)/INDEX(DADOS_MENSAIS!D:D,11),0)</f>
-        <v/>
-      </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>LTV/CAC</t>
+        </is>
+      </c>
+      <c r="C42" s="27">
+        <f>$Z$45</f>
+        <v/>
+      </c>
+      <c r="D42" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="I42" s="28">
+        <f>$Z$45</f>
+        <v/>
+      </c>
+      <c r="J42" s="29">
+        <f>IF(D42=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D42-(MIN(D42:I42)))/MAX(1E-9,(MAX(D42:I42))-(MIN(D42:I42)))*7+1,0))),1))&amp;IF(E42=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E42-(MIN(D42:I42)))/MAX(1E-9,(MAX(D42:I42))-(MIN(D42:I42)))*7+1,0))),1))&amp;IF(F42=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F42-(MIN(D42:I42)))/MAX(1E-9,(MAX(D42:I42))-(MIN(D42:I42)))*7+1,0))),1))&amp;IF(G42=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G42-(MIN(D42:I42)))/MAX(1E-9,(MAX(D42:I42))-(MIN(D42:I42)))*7+1,0))),1))&amp;IF(H42=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H42-(MIN(D42:I42)))/MAX(1E-9,(MAX(D42:I42))-(MIN(D42:I42)))*7+1,0))),1))&amp;IF(I42=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I42-(MIN(D42:I42)))/MAX(1E-9,(MAX(D42:I42))-(MIN(D42:I42)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
+      <c r="Z42" s="30">
+        <f>IFERROR(INDEX(DADOS_MENSAIS!C:C,12)/INDEX(DADOS_MENSAIS!D:D,11),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="18">
-        <f>IFERROR(INDEX(DADOS_MENSAIS!F:F,12)/INDEX(DADOS_MENSAIS!B:B,12),0)</f>
-        <v/>
-      </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+      <c r="C43" s="27">
+        <f>$Z$43</f>
+        <v/>
+      </c>
+      <c r="D43" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="E43" s="28" t="n">
+        <v>360</v>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>330</v>
+      </c>
+      <c r="G43" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>290</v>
+      </c>
+      <c r="I43" s="28">
+        <f>$Z$43</f>
+        <v/>
+      </c>
+      <c r="J43" s="29">
+        <f>IF(D43=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D43-(MIN(D43:I43)))/MAX(1E-9,(MAX(D43:I43))-(MIN(D43:I43)))*7+1,0))),1))&amp;IF(E43=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E43-(MIN(D43:I43)))/MAX(1E-9,(MAX(D43:I43))-(MIN(D43:I43)))*7+1,0))),1))&amp;IF(F43=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F43-(MIN(D43:I43)))/MAX(1E-9,(MAX(D43:I43))-(MIN(D43:I43)))*7+1,0))),1))&amp;IF(G43=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G43-(MIN(D43:I43)))/MAX(1E-9,(MAX(D43:I43))-(MIN(D43:I43)))*7+1,0))),1))&amp;IF(H43=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H43-(MIN(D43:I43)))/MAX(1E-9,(MAX(D43:I43))-(MIN(D43:I43)))*7+1,0))),1))&amp;IF(I43=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I43-(MIN(D43:I43)))/MAX(1E-9,(MAX(D43:I43))-(MIN(D43:I43)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
+      <c r="Z43" s="30">
+        <f>IFERROR(INDEX(DADOS_MENSAIS!F:F,12)/INDEX(DADOS_MENSAIS!B:B,12),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="18">
-        <f>IFERROR(INDEX(DADOS_MENSAIS!H:H,12)/MAX(B42,0.01),0)</f>
-        <v/>
-      </c>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -1568,13 +2242,14 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
+      <c r="Z44" s="30">
+        <f>IFERROR(INDEX(DADOS_MENSAIS!H:H,12)/MAX(Z42,0.01),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="18">
-        <f>IFERROR(B44/B43,0)</f>
-        <v/>
-      </c>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n"/>
@@ -1585,13 +2260,14 @@
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
+      <c r="Z45" s="30">
+        <f>IFERROR(Z44/Z43,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
-      <c r="B46" s="18">
-        <f>INDEX(DADOS_MENSAIS!D:D,12)</f>
-        <v/>
-      </c>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
@@ -1602,13 +2278,14 @@
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
+      <c r="Z46" s="30">
+        <f>INDEX(DADOS_MENSAIS!D:D,12)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
-      <c r="B47" s="18">
-        <f>INDEX(DADOS_MENSAIS!E:E,12)-INDEX(DADOS_MENSAIS!G:G,12)-INDEX(DADOS_MENSAIS!F:F,12)</f>
-        <v/>
-      </c>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="n"/>
@@ -1619,6 +2296,10 @@
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
+      <c r="Z47" s="30">
+        <f>INDEX(DADOS_MENSAIS!E:E,12)-INDEX(DADOS_MENSAIS!G:G,12)-INDEX(DADOS_MENSAIS!F:F,12)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1833,6 +2514,23 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
   </mergeCells>
+  <conditionalFormatting sqref="G30:G33">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:C43">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00C99C66"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1963,210 +2661,210 @@
       <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="33" t="n">
         <v>18000</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="33" t="n">
         <v>4200</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="33" t="n">
         <v>9000</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="33" t="n">
         <v>300</v>
       </c>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Fev</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="32" t="n">
         <v>72</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="33" t="n">
         <v>22400</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="33" t="n">
         <v>4800</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="33" t="n">
         <v>9800</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="33" t="n">
         <v>311</v>
       </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="32" t="n">
         <v>86</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="33" t="n">
         <v>27200</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="33" t="n">
         <v>5200</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="33" t="n">
         <v>10500</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="33" t="n">
         <v>316</v>
       </c>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="32" t="n">
         <v>95</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="33" t="n">
         <v>30100</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="33" t="n">
         <v>5000</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="33" t="n">
         <v>11000</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="33" t="n">
         <v>317</v>
       </c>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Mai</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="32" t="n">
         <v>111</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="33" t="n">
         <v>35600</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="33" t="n">
         <v>6100</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="33" t="n">
         <v>12000</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="33" t="n">
         <v>321</v>
       </c>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="32" t="n">
         <v>127</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="33" t="n">
         <v>41200</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="33" t="n">
         <v>6800</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="33" t="n">
         <v>12800</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="33" t="n">
         <v>324</v>
       </c>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="32" t="n">
         <v>147</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="33" t="n">
         <v>47500</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="33" t="n">
         <v>7200</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="33" t="n">
         <v>13500</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="33" t="n">
         <v>323</v>
       </c>
       <c r="I12" s="2" t="n"/>
